--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG - Relatório de Recusas  02.06.2025 a 08.06.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG - Relatório de Recusas  02.06.2025 a 08.06.2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E77A8B9E-31CC-438A-B8FF-512B782368AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04EC6B72-D3AA-4D88-AFB2-26456D7565F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="21">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,61 +54,43 @@
     <t>Relatório de Recusas  02.06.2025 a 08.06.2025</t>
   </si>
   <si>
-    <t>132676879</t>
+    <t>132704275</t>
   </si>
   <si>
     <t>1070</t>
   </si>
   <si>
-    <t>Recusas Santander 02/06/2025</t>
-  </si>
-  <si>
-    <t>132691342</t>
-  </si>
-  <si>
-    <t>132712838</t>
-  </si>
-  <si>
-    <t>132721217</t>
-  </si>
-  <si>
-    <t>132720252</t>
-  </si>
-  <si>
-    <t>132750469</t>
-  </si>
-  <si>
-    <t>132741777</t>
-  </si>
-  <si>
-    <t>132781244</t>
-  </si>
-  <si>
-    <t>132776602</t>
-  </si>
-  <si>
-    <t>132718170</t>
-  </si>
-  <si>
-    <t>132675971</t>
-  </si>
-  <si>
-    <t>132697036</t>
-  </si>
-  <si>
-    <t>132676997</t>
-  </si>
-  <si>
-    <t>132683133</t>
-  </si>
-  <si>
-    <t>132684582</t>
-  </si>
-  <si>
-    <t>132701121</t>
-  </si>
-  <si>
-    <t>132686435</t>
+    <t>Recusas Santander 03/06/2025</t>
+  </si>
+  <si>
+    <t>132722398</t>
+  </si>
+  <si>
+    <t>132716219</t>
+  </si>
+  <si>
+    <t>132739880</t>
+  </si>
+  <si>
+    <t>132740750</t>
+  </si>
+  <si>
+    <t>132781370</t>
+  </si>
+  <si>
+    <t>132771904</t>
+  </si>
+  <si>
+    <t>132701145</t>
+  </si>
+  <si>
+    <t>132703944</t>
+  </si>
+  <si>
+    <t>132704613</t>
+  </si>
+  <si>
+    <t>132707276</t>
   </si>
 </sst>
 </file>
@@ -515,7 +497,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -627,7 +609,7 @@
       <c r="C6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="2" t="s">
@@ -681,7 +663,7 @@
       <c r="C9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="6" t="s">
         <v>7</v>
       </c>
       <c r="E9" s="2" t="s">
@@ -699,7 +681,7 @@
       <c r="C10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E10" s="2" t="s">
@@ -735,7 +717,7 @@
       <c r="C12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="6" t="s">
         <v>7</v>
       </c>
       <c r="E12" s="2" t="s">
@@ -744,111 +726,24 @@
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="D13" s="6"/>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="D14" s="6"/>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="D15" s="6"/>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="D16" s="6"/>
       <c r="F16"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="17" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D17" s="6"/>
       <c r="F17"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
